--- a/database/seeders/data/station.xlsx
+++ b/database/seeders/data/station.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\sdo_ilagan_attendance_monitoring\database\seeders\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0B82827-7EAF-4423-9158-FB576BFD8459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF55BB7-A675-4F0B-80CB-D93FEBFE7E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{FEB79122-6E29-41B3-B49F-3A543614FD39}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FEB79122-6E29-41B3-B49F-3A543614FD39}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
   <si>
     <t>Code</t>
   </si>
@@ -336,10 +336,16 @@
     <t>Station Name</t>
   </si>
   <si>
-    <t>School Division Office</t>
-  </si>
-  <si>
-    <t>SDO</t>
+    <t>SDO - AO</t>
+  </si>
+  <si>
+    <t>School Division Office - Administrative Office</t>
+  </si>
+  <si>
+    <t>SDO - HRMO</t>
+  </si>
+  <si>
+    <t>School Division Office - Human Resource Management Office</t>
   </si>
 </sst>
 </file>
@@ -416,9 +422,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -456,7 +462,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -562,7 +568,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -704,7 +710,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -712,14 +718,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5882D283-30F4-457F-97EB-B1DC9BBDCEAF}">
-  <dimension ref="A1:B100"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B101"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -727,795 +733,803 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" t="s">
         <v>101</v>
       </c>
-      <c r="B2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
         <v>305727</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
         <v>103384</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
         <v>103412</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
         <v>300545</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
         <v>103354</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
         <v>501839</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
         <v>103356</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
         <v>103413</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
         <v>103414</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
         <v>103365</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
         <v>103415</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
         <v>103357</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B15" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
         <v>103385</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B16" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
         <v>155505</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B17" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
         <v>103387</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B18" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
         <v>103359</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B19" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
         <v>103416</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B20" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
         <v>103417</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B21" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
-        <v>103419</v>
-      </c>
-      <c r="B21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>103419</v>
       </c>
       <c r="B22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <v>103419</v>
+      </c>
+      <c r="B23" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
         <v>103388</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B24" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
         <v>103389</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B25" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
         <v>103390</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B26" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
         <v>103392</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B27" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
         <v>103393</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B28" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
         <v>103395</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B29" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
         <v>103391</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B30" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
         <v>103386</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B31" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
         <v>155506</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B32" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
         <v>103420</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B33" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="2">
         <v>103361</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B34" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="2">
         <v>103362</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B35" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="2">
         <v>103396</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B36" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="2">
         <v>103421</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B37" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="2">
         <v>103397</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B38" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="2">
         <v>501548</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B39" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="2">
         <v>103399</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B40" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="2">
         <v>103363</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B41" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="2">
         <v>103400</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B42" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="2">
         <v>500087</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B43" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="2">
         <v>103422</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B44" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="2">
         <v>500992</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B45" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="2">
         <v>103402</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B46" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
         <v>103423</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B47" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
         <v>300540</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B48" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="2">
         <v>300542</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B49" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="2">
         <v>306105</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B50" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="2">
         <v>306149</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B51" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="2">
         <v>103424</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B52" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="2">
         <v>500080</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B53" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="2">
         <v>103425</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B54" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="2">
         <v>103426</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B55" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" s="2">
         <v>500078</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B56" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" s="2">
         <v>103427</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B57" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" s="2">
         <v>103366</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B58" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" s="2">
         <v>103367</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B59" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" s="2">
         <v>103368</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B60" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" s="2">
         <v>103369</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B61" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" s="2">
         <v>103370</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B62" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" s="2">
         <v>103428</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B63" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" s="2">
         <v>103429</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B64" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" s="2">
         <v>103371</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B65" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" s="2">
         <v>103404</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B66" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" s="2">
         <v>103372</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B67" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" s="2">
         <v>103430</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B68" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" s="2">
         <v>103373</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B69" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" s="2">
         <v>300543</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B70" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" s="2">
         <v>103405</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B71" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" s="2">
         <v>103431</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B72" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="3">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" s="3">
         <v>103374</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B73" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="2">
         <v>103406</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B74" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="2">
         <v>300583</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B75" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="2">
         <v>103432</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B76" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="2">
         <v>103433</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B77" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="2">
         <v>103375</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B78" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="3">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="3">
         <v>500018</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B79" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="2">
         <v>103394</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B80" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" s="2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="2">
         <v>155519</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B81" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" s="2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" s="2">
         <v>500074</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B82" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" s="2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" s="2">
         <v>103408</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B83" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" s="2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" s="2">
         <v>300584</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B84" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" s="2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" s="2">
         <v>103377</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B85" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" s="2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" s="2">
         <v>103434</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B86" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" s="2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" s="2">
         <v>500731</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B87" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" s="2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" s="2">
         <v>155527</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B88" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" s="2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" s="2">
         <v>103411</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B89" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" s="2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" s="2">
         <v>103378</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B90" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90" s="2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" s="2">
         <v>103379</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B91" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91" s="2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" s="2">
         <v>300602</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B92" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92" s="2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" s="2">
         <v>103435</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B93" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93" s="2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94" s="2">
         <v>103436</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B94" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94" s="2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95" s="2">
         <v>103409</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B95" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95" s="2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96" s="2">
         <v>103380</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B96" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A96" s="2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97" s="2">
         <v>103437</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B97" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97" s="2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98" s="2">
         <v>103381</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B98" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98" s="2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A99" s="2">
         <v>103382</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B99" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A99" s="2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100" s="2">
         <v>103438</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B100" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A100" s="2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A101" s="2">
         <v>103383</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B101" t="s">
         <v>98</v>
       </c>
     </row>
